--- a/evaluation/test_questions.xlsx
+++ b/evaluation/test_questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f1ad9b415b81f28d/Desktop/Master/WBH/3. Semester/Forschungsarbeit inkl. Fachseminar/text_to_sql_prototype/evaluation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="160" documentId="11_AD4DB114E441178AC67DF40AF693DEDE693EDF18" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F86B5835-03FC-4D2B-9B5D-2D7B238701D2}"/>
+  <xr:revisionPtr revIDLastSave="172" documentId="11_AD4DB114E441178AC67DF40AF693DEDE693EDF18" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FF22CF0-44FB-4663-A90E-593325D03054}"/>
   <bookViews>
-    <workbookView xWindow="12450" yWindow="0" windowWidth="16455" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -425,7 +425,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -443,12 +443,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -735,7 +729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.5703125" customWidth="1"/>
@@ -770,74 +764,82 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+    <row r="3" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="D6" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>11</v>
@@ -848,24 +850,24 @@
     </row>
     <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>19</v>
+        <v>82</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>11</v>
@@ -874,222 +876,222 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+    <row r="11" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B11" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C11" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>86</v>
+        <v>31</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D19" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D21" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="6" t="s">
+    <row r="24" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>11</v>
@@ -1098,12 +1100,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>11</v>
@@ -1112,29 +1114,29 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>10</v>
@@ -1142,24 +1144,24 @@
     </row>
     <row r="30" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>26</v>
@@ -1168,40 +1170,40 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C32" s="4" t="s">
+    <row r="32" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C32" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>11</v>
@@ -1210,40 +1212,40 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="A36" s="5" t="s">
+    <row r="35" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B35" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C36" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D36" s="6" t="s">
+      <c r="C35" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>11</v>
@@ -1252,12 +1254,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>11</v>
@@ -1266,12 +1268,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>11</v>
@@ -1280,29 +1282,29 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>21</v>
@@ -1310,13 +1312,13 @@
     </row>
     <row r="42" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>21</v>
@@ -1324,10 +1326,10 @@
     </row>
     <row r="43" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>26</v>
@@ -1338,10 +1340,10 @@
     </row>
     <row r="44" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>26</v>
@@ -1352,10 +1354,10 @@
     </row>
     <row r="45" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>26</v>
@@ -1364,82 +1366,82 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C46" s="4" t="s">
+    <row r="46" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A46" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C46" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C47" s="6" t="s">
+    <row r="47" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C47" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D47" s="6" t="s">
+      <c r="D47" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C49" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C50" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D50" s="4" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>26</v>
@@ -1448,27 +1450,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
